--- a/output/graficos_nacionales/plot_nacional_e_preneta_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_preneta_a_2021.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J274"/>
+  <dimension ref="A1:J278"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -596,21 +596,21 @@
         <v>2021</v>
       </c>
       <c r="B6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>11201</t>
+          <t>12401</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Natales</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="I6">
-        <v>70.7239</v>
+        <v>71.46666999999999</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -651,12 +651,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>11101</t>
+          <t>11201</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Coyhaique</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="I7">
-        <v>70.51782</v>
+        <v>70.7239</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -697,12 +697,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>11102</t>
+          <t>11101</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lago Verde</t>
+          <t>Coyhaique</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="I8">
-        <v>68.75</v>
+        <v>70.51782</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -734,31 +734,31 @@
         <v>2021</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7303</t>
+          <t>11102</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Licantén</t>
+          <t>Lago Verde</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>centro</t>
+          <t>austral</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Macrozona Centro</t>
+          <t>Macrozona Austral</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="I9">
-        <v>72.32375999999999</v>
+        <v>68.75</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -780,31 +780,31 @@
         <v>2021</v>
       </c>
       <c r="B10">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>16109</t>
+          <t>12302</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Yungay</t>
+          <t>Primavera</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>centro</t>
+          <t>austral</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Macrozona Centro</t>
+          <t>Macrozona Austral</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="I10">
-        <v>68.70229</v>
+        <v>66.66667</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -826,31 +826,31 @@
         <v>2021</v>
       </c>
       <c r="B11">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>7202</t>
+          <t>12101</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chanco</t>
+          <t>Punta Arenas</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>centro</t>
+          <t>austral</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Macrozona Centro</t>
+          <t>Macrozona Austral</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="I11">
-        <v>68.61597999999999</v>
+        <v>63.69542</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -872,31 +872,31 @@
         <v>2021</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7401</t>
+          <t>12103</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Linares</t>
+          <t>Río Verde</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>centro</t>
+          <t>austral</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Macrozona Centro</t>
+          <t>Macrozona Austral</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -905,7 +905,7 @@
         </is>
       </c>
       <c r="I12">
-        <v>68.43843</v>
+        <v>63.63636</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -927,12 +927,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>7307</t>
+          <t>7303</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sagrada Familia</t>
+          <t>Licantén</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="I13">
-        <v>68.36006999999999</v>
+        <v>72.32375999999999</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -964,21 +964,21 @@
         <v>2021</v>
       </c>
       <c r="B14">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7104</t>
+          <t>16109</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Empedrado</t>
+          <t>Yungay</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="I14">
-        <v>68.33977</v>
+        <v>68.70229</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1010,21 +1010,21 @@
         <v>2021</v>
       </c>
       <c r="B15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>6307</t>
+          <t>7202</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Peralillo</t>
+          <t>Chanco</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="I15">
-        <v>67.74691</v>
+        <v>68.61597999999999</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1056,21 +1056,21 @@
         <v>2021</v>
       </c>
       <c r="B16">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>16205</t>
+          <t>7401</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Portezuelo</t>
+          <t>Linares</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="I16">
-        <v>67.68061</v>
+        <v>68.43843</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7302</t>
+          <t>7307</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hualañé</t>
+          <t>Sagrada Familia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="I17">
-        <v>67.55725</v>
+        <v>68.36006999999999</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1148,21 +1148,21 @@
         <v>2021</v>
       </c>
       <c r="B18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>5702</t>
+          <t>7104</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Catemu</t>
+          <t>Empedrado</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="I18">
-        <v>66.51736</v>
+        <v>68.33977</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1194,21 +1194,21 @@
         <v>2021</v>
       </c>
       <c r="B19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>6307</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Villa Alegre</t>
+          <t>Peralillo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="I19">
-        <v>65.85858</v>
+        <v>67.74691</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1240,21 +1240,21 @@
         <v>2021</v>
       </c>
       <c r="B20">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>7304</t>
+          <t>16205</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Molina</t>
+          <t>Portezuelo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="I20">
-        <v>64.91531000000001</v>
+        <v>67.68061</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1286,21 +1286,21 @@
         <v>2021</v>
       </c>
       <c r="B21">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>16201</t>
+          <t>7302</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Quirihue</t>
+          <t>Hualañé</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="I21">
-        <v>64.16665999999999</v>
+        <v>67.55725</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1332,21 +1332,21 @@
         <v>2021</v>
       </c>
       <c r="B22">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>7103</t>
+          <t>5702</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Curepto</t>
+          <t>Catemu</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="I22">
-        <v>63.71134</v>
+        <v>66.51736</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pelarco</t>
+          <t>Villa Alegre</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="I23">
-        <v>63.6218</v>
+        <v>65.85858</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1433,12 +1433,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>7402</t>
+          <t>7304</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Colbún</t>
+          <t>Molina</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="I24">
-        <v>63.5234</v>
+        <v>64.91531000000001</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1479,12 +1479,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>16207</t>
+          <t>16201</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Treguaco</t>
+          <t>Quirihue</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="I25">
-        <v>63.25088</v>
+        <v>64.16665999999999</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1516,21 +1516,21 @@
         <v>2021</v>
       </c>
       <c r="B26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>5704</t>
+          <t>7103</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Panquehue</t>
+          <t>Curepto</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="I26">
-        <v>63.242</v>
+        <v>63.71134</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1571,12 +1571,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>7305</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rauco</t>
+          <t>Pelarco</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="I27">
-        <v>63.19759</v>
+        <v>63.6218</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1608,21 +1608,21 @@
         <v>2021</v>
       </c>
       <c r="B28">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>16103</t>
+          <t>7402</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chillán Viejo</t>
+          <t>Colbún</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="I28">
-        <v>62.82051</v>
+        <v>63.5234</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1654,21 +1654,21 @@
         <v>2021</v>
       </c>
       <c r="B29">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>7306</t>
+          <t>16207</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Romeral</t>
+          <t>Treguaco</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="I29">
-        <v>62.76694</v>
+        <v>63.25088</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1700,21 +1700,21 @@
         <v>2021</v>
       </c>
       <c r="B30">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>7408</t>
+          <t>5704</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Yerbas Buenas</t>
+          <t>Panquehue</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="I30">
-        <v>62.65876</v>
+        <v>63.242</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         <v>2021</v>
       </c>
       <c r="B31">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>16105</t>
+          <t>7305</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pemuco</t>
+          <t>Rauco</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="I31">
-        <v>62.44898</v>
+        <v>63.19759</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1792,21 +1792,21 @@
         <v>2021</v>
       </c>
       <c r="B32">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>6202</t>
+          <t>16103</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>La Estrella</t>
+          <t>Chillán Viejo</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="I32">
-        <v>62.37624</v>
+        <v>62.82051</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -1838,21 +1838,21 @@
         <v>2021</v>
       </c>
       <c r="B33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>5404</t>
+          <t>7306</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Petorca</t>
+          <t>Romeral</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="I33">
-        <v>62.05036</v>
+        <v>62.76694</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -1893,12 +1893,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>7403</t>
+          <t>7408</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Longaví</t>
+          <t>Yerbas Buenas</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="I34">
-        <v>61.99299</v>
+        <v>62.65876</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -1939,12 +1939,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>16102</t>
+          <t>16105</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bulnes</t>
+          <t>Pemuco</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="I35">
-        <v>61.88235</v>
+        <v>62.44898</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -1976,21 +1976,21 @@
         <v>2021</v>
       </c>
       <c r="B36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>5705</t>
+          <t>6202</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Putaendo</t>
+          <t>La Estrella</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="I36">
-        <v>61.69643</v>
+        <v>62.37624</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2022,21 +2022,21 @@
         <v>2021</v>
       </c>
       <c r="B37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>6302</t>
+          <t>5404</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Chépica</t>
+          <t>Petorca</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2055,7 +2055,7 @@
         </is>
       </c>
       <c r="I37">
-        <v>61.68981</v>
+        <v>62.05036</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2077,12 +2077,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>7107</t>
+          <t>7403</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Pencahue</t>
+          <t>Longaví</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="I38">
-        <v>61.62528</v>
+        <v>61.99299</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2114,21 +2114,21 @@
         <v>2021</v>
       </c>
       <c r="B39">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>7102</t>
+          <t>16102</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Constitución</t>
+          <t>Bulnes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2147,7 +2147,7 @@
         </is>
       </c>
       <c r="I39">
-        <v>61.57191</v>
+        <v>61.88235</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2169,12 +2169,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>5405</t>
+          <t>5705</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Zapallar</t>
+          <t>Putaendo</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2193,7 +2193,7 @@
         </is>
       </c>
       <c r="I40">
-        <v>61.16838</v>
+        <v>61.69643</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -2206,21 +2206,21 @@
         <v>2021</v>
       </c>
       <c r="B41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>7404</t>
+          <t>6302</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Parral</t>
+          <t>Chépica</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2239,7 +2239,7 @@
         </is>
       </c>
       <c r="I41">
-        <v>61.07102</v>
+        <v>61.68981</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -2252,21 +2252,21 @@
         <v>2021</v>
       </c>
       <c r="B42">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>5105</t>
+          <t>7107</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Puchuncaví</t>
+          <t>Pencahue</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2285,7 +2285,7 @@
         </is>
       </c>
       <c r="I42">
-        <v>60.90283</v>
+        <v>61.62528</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2307,12 +2307,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>7108</t>
+          <t>7102</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Río Claro</t>
+          <t>Constitución</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="I43">
-        <v>60.5848</v>
+        <v>61.57191</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2344,21 +2344,21 @@
         <v>2021</v>
       </c>
       <c r="B44">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>7405</t>
+          <t>5405</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Retiro</t>
+          <t>Zapallar</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="I44">
-        <v>60.55901</v>
+        <v>61.16838</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2399,12 +2399,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>7203</t>
+          <t>7404</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Pelluhue</t>
+          <t>Parral</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2423,7 +2423,7 @@
         </is>
       </c>
       <c r="I45">
-        <v>60.4</v>
+        <v>61.07102</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>5403</t>
+          <t>5105</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Papudo</t>
+          <t>Puchuncaví</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2469,7 +2469,7 @@
         </is>
       </c>
       <c r="I46">
-        <v>60.15424</v>
+        <v>60.90283</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2482,21 +2482,21 @@
         <v>2021</v>
       </c>
       <c r="B47">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>16204</t>
+          <t>7108</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ninhue</t>
+          <t>Río Claro</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="I47">
-        <v>60</v>
+        <v>60.5848</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -2528,21 +2528,21 @@
         <v>2021</v>
       </c>
       <c r="B48">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>16101</t>
+          <t>7405</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Chillán</t>
+          <t>Retiro</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="I48">
-        <v>59.89243</v>
+        <v>60.55901</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -2583,12 +2583,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>7406</t>
+          <t>7203</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>San Javier</t>
+          <t>Pelluhue</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="I49">
-        <v>59.75733</v>
+        <v>60.4</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -2629,12 +2629,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>5403</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Calle Larga</t>
+          <t>Papudo</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="I50">
-        <v>59.63801</v>
+        <v>60.15424</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -2666,21 +2666,21 @@
         <v>2021</v>
       </c>
       <c r="B51">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>7301</t>
+          <t>16204</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Curicó</t>
+          <t>Ninhue</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2699,7 +2699,7 @@
         </is>
       </c>
       <c r="I51">
-        <v>59.60222</v>
+        <v>60</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -2712,21 +2712,21 @@
         <v>2021</v>
       </c>
       <c r="B52">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>7110</t>
+          <t>16101</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>San Rafael</t>
+          <t>Chillán</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2745,7 +2745,7 @@
         </is>
       </c>
       <c r="I52">
-        <v>59.39849</v>
+        <v>59.89243</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -2758,21 +2758,21 @@
         <v>2021</v>
       </c>
       <c r="B53">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>16302</t>
+          <t>7406</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Coihueco</t>
+          <t>San Javier</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2791,7 +2791,7 @@
         </is>
       </c>
       <c r="I53">
-        <v>59.38256</v>
+        <v>59.75733</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -2804,21 +2804,21 @@
         <v>2021</v>
       </c>
       <c r="B54">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>San Fernando</t>
+          <t>Calle Larga</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2837,7 +2837,7 @@
         </is>
       </c>
       <c r="I54">
-        <v>59.37763</v>
+        <v>59.63801</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -2859,12 +2859,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>7301</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Vichuquén</t>
+          <t>Curicó</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="I55">
-        <v>59.33014</v>
+        <v>59.60222</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -2896,21 +2896,21 @@
         <v>2021</v>
       </c>
       <c r="B56">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>6105</t>
+          <t>7110</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Doñihue</t>
+          <t>San Rafael</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="I56">
-        <v>59.3185</v>
+        <v>59.39849</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -2942,21 +2942,21 @@
         <v>2021</v>
       </c>
       <c r="B57">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>6305</t>
+          <t>16302</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Nancagua</t>
+          <t>Coihueco</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2975,7 +2975,7 @@
         </is>
       </c>
       <c r="I57">
-        <v>58.84995</v>
+        <v>59.38256</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -2988,21 +2988,21 @@
         <v>2021</v>
       </c>
       <c r="B58">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>5803</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Olmué</t>
+          <t>San Fernando</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="I58">
-        <v>58.62355</v>
+        <v>59.37763</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -3043,12 +3043,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>7308</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Teno</t>
+          <t>Vichuquén</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="I59">
-        <v>58.59331</v>
+        <v>59.33014</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -3080,21 +3080,21 @@
         <v>2021</v>
       </c>
       <c r="B60">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>5506</t>
+          <t>6105</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Nogales</t>
+          <t>Doñihue</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3113,7 +3113,7 @@
         </is>
       </c>
       <c r="I60">
-        <v>58.48641</v>
+        <v>59.3185</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>6310</t>
+          <t>6305</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Nancagua</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3159,7 +3159,7 @@
         </is>
       </c>
       <c r="I61">
-        <v>58.26547</v>
+        <v>58.84995</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -3172,21 +3172,21 @@
         <v>2021</v>
       </c>
       <c r="B62">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>6114</t>
+          <t>5803</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Quinta de Tilcoco</t>
+          <t>Olmué</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="I62">
-        <v>58.18859</v>
+        <v>58.62355</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -3218,21 +3218,21 @@
         <v>2021</v>
       </c>
       <c r="B63">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>16305</t>
+          <t>7308</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>San Nicolás</t>
+          <t>Teno</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="I63">
-        <v>58.07327</v>
+        <v>58.59331</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -3264,21 +3264,21 @@
         <v>2021</v>
       </c>
       <c r="B64">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>7109</t>
+          <t>5506</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>San Clemente</t>
+          <t>Nogales</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="I64">
-        <v>58.03922</v>
+        <v>58.48641</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -3310,21 +3310,21 @@
         <v>2021</v>
       </c>
       <c r="B65">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>16106</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Pinto</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3343,7 +3343,7 @@
         </is>
       </c>
       <c r="I65">
-        <v>57.84172</v>
+        <v>58.26547</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -3356,21 +3356,21 @@
         <v>2021</v>
       </c>
       <c r="B66">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>7201</t>
+          <t>6114</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Cauquenes</t>
+          <t>Quinta de Tilcoco</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3389,7 +3389,7 @@
         </is>
       </c>
       <c r="I66">
-        <v>57.78612</v>
+        <v>58.18859</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -3402,21 +3402,21 @@
         <v>2021</v>
       </c>
       <c r="B67">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>6115</t>
+          <t>16305</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Rengo</t>
+          <t>San Nicolás</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="I67">
-        <v>57.7327</v>
+        <v>58.07327</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -3448,21 +3448,21 @@
         <v>2021</v>
       </c>
       <c r="B68">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>6116</t>
+          <t>7109</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Requínoa</t>
+          <t>San Clemente</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3481,7 +3481,7 @@
         </is>
       </c>
       <c r="I68">
-        <v>57.65718</v>
+        <v>58.03922</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -3503,12 +3503,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>16301</t>
+          <t>16106</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>San Carlos</t>
+          <t>Pinto</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="I69">
-        <v>57.35775</v>
+        <v>57.84172</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -3540,21 +3540,21 @@
         <v>2021</v>
       </c>
       <c r="B70">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>7201</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Cabildo</t>
+          <t>Cauquenes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="I70">
-        <v>57.29866</v>
+        <v>57.78612</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -3586,21 +3586,21 @@
         <v>2021</v>
       </c>
       <c r="B71">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>16107</t>
+          <t>6115</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Quillón</t>
+          <t>Rengo</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="I71">
-        <v>57.26028</v>
+        <v>57.7327</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -3632,21 +3632,21 @@
         <v>2021</v>
       </c>
       <c r="B72">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>5601</t>
+          <t>6116</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Requínoa</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="I72">
-        <v>57.26004</v>
+        <v>57.65718</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -3678,21 +3678,21 @@
         <v>2021</v>
       </c>
       <c r="B73">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>6103</t>
+          <t>16301</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Coinco</t>
+          <t>San Carlos</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="I73">
-        <v>57.0499</v>
+        <v>57.35775</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -3724,21 +3724,21 @@
         <v>2021</v>
       </c>
       <c r="B74">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Placilla</t>
+          <t>Cabildo</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="I74">
-        <v>56.87732</v>
+        <v>57.29866</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -3770,21 +3770,21 @@
         <v>2021</v>
       </c>
       <c r="B75">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>6112</t>
+          <t>16107</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Peumo</t>
+          <t>Quillón</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="I75">
-        <v>56.68639</v>
+        <v>57.26028</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -3816,21 +3816,21 @@
         <v>2021</v>
       </c>
       <c r="B76">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>13121</t>
+          <t>5601</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Pedro Aguirre Cerda</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="I76">
-        <v>56.681</v>
+        <v>57.26004</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -3862,21 +3862,21 @@
         <v>2021</v>
       </c>
       <c r="B77">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>13128</t>
+          <t>6103</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Renca</t>
+          <t>Coinco</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="I77">
-        <v>56.6382</v>
+        <v>57.0499</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -3908,21 +3908,21 @@
         <v>2021</v>
       </c>
       <c r="B78">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>6308</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Calera</t>
+          <t>Placilla</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3941,7 +3941,7 @@
         </is>
       </c>
       <c r="I78">
-        <v>56.5635</v>
+        <v>56.87732</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -3954,21 +3954,21 @@
         <v>2021</v>
       </c>
       <c r="B79">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>6112</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Quillota</t>
+          <t>Peumo</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3987,7 +3987,7 @@
         </is>
       </c>
       <c r="I79">
-        <v>56.38641</v>
+        <v>56.68639</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -4000,21 +4000,21 @@
         <v>2021</v>
       </c>
       <c r="B80">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>16202</t>
+          <t>13121</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Cobquecura</t>
+          <t>Pedro Aguirre Cerda</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4033,7 +4033,7 @@
         </is>
       </c>
       <c r="I80">
-        <v>56.33188</v>
+        <v>56.681</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>13202</t>
+          <t>13128</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Pirque</t>
+          <t>Renca</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4079,7 +4079,7 @@
         </is>
       </c>
       <c r="I81">
-        <v>56.31941</v>
+        <v>56.6382</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -4092,21 +4092,21 @@
         <v>2021</v>
       </c>
       <c r="B82">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>6303</t>
+          <t>5502</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Chimbarongo</t>
+          <t>Calera</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -4125,7 +4125,7 @@
         </is>
       </c>
       <c r="I82">
-        <v>56.27393</v>
+        <v>56.5635</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -4147,12 +4147,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>5701</t>
+          <t>5501</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>San Felipe</t>
+          <t>Quillota</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4171,7 +4171,7 @@
         </is>
       </c>
       <c r="I83">
-        <v>56.23833</v>
+        <v>56.38641</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -4193,12 +4193,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>16108</t>
+          <t>16202</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>San Ignacio</t>
+          <t>Cobquecura</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="I84">
-        <v>56.22933</v>
+        <v>56.33188</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -4230,21 +4230,21 @@
         <v>2021</v>
       </c>
       <c r="B85">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>7101</t>
+          <t>13202</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Talca</t>
+          <t>Pirque</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4263,7 +4263,7 @@
         </is>
       </c>
       <c r="I85">
-        <v>56.17088</v>
+        <v>56.31941</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -4276,21 +4276,21 @@
         <v>2021</v>
       </c>
       <c r="B86">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>13111</t>
+          <t>6303</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>La Granja</t>
+          <t>Chimbarongo</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4309,7 +4309,7 @@
         </is>
       </c>
       <c r="I86">
-        <v>56.07937</v>
+        <v>56.27393</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -4322,21 +4322,21 @@
         <v>2021</v>
       </c>
       <c r="B87">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>6117</t>
+          <t>5701</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>San Vicente</t>
+          <t>San Felipe</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4355,7 +4355,7 @@
         </is>
       </c>
       <c r="I87">
-        <v>55.67159</v>
+        <v>56.23833</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -4368,21 +4368,21 @@
         <v>2021</v>
       </c>
       <c r="B88">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>5606</t>
+          <t>16108</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Santo Domingo</t>
+          <t>San Ignacio</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="I88">
-        <v>55.63187</v>
+        <v>56.22933</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -4414,21 +4414,21 @@
         <v>2021</v>
       </c>
       <c r="B89">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>6203</t>
+          <t>7101</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Litueche</t>
+          <t>Talca</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="I89">
-        <v>55.5332</v>
+        <v>56.17088</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -4469,12 +4469,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>13403</t>
+          <t>13111</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Calera de Tango</t>
+          <t>La Granja</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="I90">
-        <v>55.14834</v>
+        <v>56.07937</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -4506,21 +4506,21 @@
         <v>2021</v>
       </c>
       <c r="B91">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>16304</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>San Fabián</t>
+          <t>San Vicente</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4539,7 +4539,7 @@
         </is>
       </c>
       <c r="I91">
-        <v>55.13699</v>
+        <v>55.67159</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -4561,12 +4561,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5606</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Santo Domingo</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4585,7 +4585,7 @@
         </is>
       </c>
       <c r="I92">
-        <v>55.12754</v>
+        <v>55.63187</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -4598,21 +4598,21 @@
         <v>2021</v>
       </c>
       <c r="B93">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>13105</t>
+          <t>6203</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>El Bosque</t>
+          <t>Litueche</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4631,7 +4631,7 @@
         </is>
       </c>
       <c r="I93">
-        <v>55.1146</v>
+        <v>55.5332</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -4644,21 +4644,21 @@
         <v>2021</v>
       </c>
       <c r="B94">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>5503</t>
+          <t>13403</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Hijuelas</t>
+          <t>Calera de Tango</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="I94">
-        <v>54.99207</v>
+        <v>55.14834</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -4690,21 +4690,21 @@
         <v>2021</v>
       </c>
       <c r="B95">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>6113</t>
+          <t>16304</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Pichidegua</t>
+          <t>San Fabián</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4723,7 +4723,7 @@
         </is>
       </c>
       <c r="I95">
-        <v>54.96688</v>
+        <v>55.13699</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -4736,21 +4736,21 @@
         <v>2021</v>
       </c>
       <c r="B96">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>16104</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>El Carmen</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="I96">
-        <v>54.94653</v>
+        <v>55.12754</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -4782,21 +4782,21 @@
         <v>2021</v>
       </c>
       <c r="B97">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>6304</t>
+          <t>13105</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Lolol</t>
+          <t>El Bosque</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="I97">
-        <v>54.83871</v>
+        <v>55.1146</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -4828,21 +4828,21 @@
         <v>2021</v>
       </c>
       <c r="B98">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>13131</t>
+          <t>5503</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>San Ramón</t>
+          <t>Hijuelas</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4861,7 +4861,7 @@
         </is>
       </c>
       <c r="I98">
-        <v>54.83034</v>
+        <v>54.99207</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -4874,21 +4874,21 @@
         <v>2021</v>
       </c>
       <c r="B99">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>13503</t>
+          <t>6113</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Curacaví</t>
+          <t>Pichidegua</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4907,7 +4907,7 @@
         </is>
       </c>
       <c r="I99">
-        <v>54.53721</v>
+        <v>54.96688</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -4920,21 +4920,21 @@
         <v>2021</v>
       </c>
       <c r="B100">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>13116</t>
+          <t>16104</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Lo Espejo</t>
+          <t>El Carmen</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -4953,7 +4953,7 @@
         </is>
       </c>
       <c r="I100">
-        <v>54.42924</v>
+        <v>54.94653</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -4975,12 +4975,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>6106</t>
+          <t>6304</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Graneros</t>
+          <t>Lolol</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4999,7 +4999,7 @@
         </is>
       </c>
       <c r="I101">
-        <v>54.39936</v>
+        <v>54.83871</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -5012,21 +5012,21 @@
         <v>2021</v>
       </c>
       <c r="B102">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>5802</t>
+          <t>13131</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Limache</t>
+          <t>San Ramón</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -5045,7 +5045,7 @@
         </is>
       </c>
       <c r="I102">
-        <v>54.3865</v>
+        <v>54.83034</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -5058,21 +5058,21 @@
         <v>2021</v>
       </c>
       <c r="B103">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>13503</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>La Ligua</t>
+          <t>Curacaví</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="I103">
-        <v>54.06061</v>
+        <v>54.53721</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -5113,12 +5113,12 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>13203</t>
+          <t>13116</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>San José de Maipo</t>
+          <t>Lo Espejo</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="I104">
-        <v>53.86792</v>
+        <v>54.42924</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -5159,12 +5159,12 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>6111</t>
+          <t>6106</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Olivar</t>
+          <t>Graneros</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5183,7 +5183,7 @@
         </is>
       </c>
       <c r="I105">
-        <v>53.76106</v>
+        <v>54.39936</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -5196,21 +5196,21 @@
         <v>2021</v>
       </c>
       <c r="B106">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>6104</t>
+          <t>5802</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Coltauco</t>
+          <t>Limache</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -5229,7 +5229,7 @@
         </is>
       </c>
       <c r="I106">
-        <v>53.75552</v>
+        <v>54.3865</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -5251,12 +5251,12 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>5107</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Quintero</t>
+          <t>La Ligua</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="I107">
-        <v>53.73272</v>
+        <v>54.06061</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -5288,21 +5288,21 @@
         <v>2021</v>
       </c>
       <c r="B108">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>6109</t>
+          <t>13203</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Malloa</t>
+          <t>San José de Maipo</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -5321,7 +5321,7 @@
         </is>
       </c>
       <c r="I108">
-        <v>53.73135</v>
+        <v>53.86792</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -5334,21 +5334,21 @@
         <v>2021</v>
       </c>
       <c r="B109">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Casablanca</t>
+          <t>Olivar</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -5367,7 +5367,7 @@
         </is>
       </c>
       <c r="I109">
-        <v>53.55785</v>
+        <v>53.76106</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -5380,21 +5380,21 @@
         <v>2021</v>
       </c>
       <c r="B110">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>13103</t>
+          <t>6104</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Cerro Navia</t>
+          <t>Coltauco</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="I110">
-        <v>53.3644</v>
+        <v>53.75552</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -5426,21 +5426,21 @@
         <v>2021</v>
       </c>
       <c r="B111">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>6110</t>
+          <t>5107</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Mostazal</t>
+          <t>Quintero</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -5459,7 +5459,7 @@
         </is>
       </c>
       <c r="I111">
-        <v>53.30882</v>
+        <v>53.73272</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -5472,21 +5472,21 @@
         <v>2021</v>
       </c>
       <c r="B112">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>5804</t>
+          <t>6109</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Villa Alemana</t>
+          <t>Malloa</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -5505,7 +5505,7 @@
         </is>
       </c>
       <c r="I112">
-        <v>52.86344</v>
+        <v>53.73135</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -5518,21 +5518,21 @@
         <v>2021</v>
       </c>
       <c r="B113">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>13102</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Cerrillos</t>
+          <t>Casablanca</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -5551,7 +5551,7 @@
         </is>
       </c>
       <c r="I113">
-        <v>52.58964</v>
+        <v>53.55785</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -5564,21 +5564,21 @@
         <v>2021</v>
       </c>
       <c r="B114">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>5504</t>
+          <t>13103</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>La Cruz</t>
+          <t>Cerro Navia</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -5597,7 +5597,7 @@
         </is>
       </c>
       <c r="I114">
-        <v>52.56724</v>
+        <v>53.3644</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -5610,21 +5610,21 @@
         <v>2021</v>
       </c>
       <c r="B115">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>13118</t>
+          <t>6110</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Macul</t>
+          <t>Mostazal</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -5643,7 +5643,7 @@
         </is>
       </c>
       <c r="I115">
-        <v>52.45783</v>
+        <v>53.30882</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -5656,21 +5656,21 @@
         <v>2021</v>
       </c>
       <c r="B116">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>13129</t>
+          <t>5804</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>San Joaquín</t>
+          <t>Villa Alemana</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -5689,7 +5689,7 @@
         </is>
       </c>
       <c r="I116">
-        <v>51.85805</v>
+        <v>52.86344</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -5702,21 +5702,21 @@
         <v>2021</v>
       </c>
       <c r="B117">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>6101</t>
+          <t>13102</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Rancagua</t>
+          <t>Cerrillos</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="I117">
-        <v>51.83538</v>
+        <v>52.58964</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>5103</t>
+          <t>5504</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Concón</t>
+          <t>La Cruz</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -5781,7 +5781,7 @@
         </is>
       </c>
       <c r="I118">
-        <v>51.731</v>
+        <v>52.56724</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>13117</t>
+          <t>13118</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Lo Prado</t>
+          <t>Macul</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -5827,7 +5827,7 @@
         </is>
       </c>
       <c r="I119">
-        <v>51.72179</v>
+        <v>52.45783</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -5840,21 +5840,21 @@
         <v>2021</v>
       </c>
       <c r="B120">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t>13129</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Quilpué</t>
+          <t>San Joaquín</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -5873,7 +5873,7 @@
         </is>
       </c>
       <c r="I120">
-        <v>51.60676</v>
+        <v>51.85805</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -5886,21 +5886,21 @@
         <v>2021</v>
       </c>
       <c r="B121">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>13404</t>
+          <t>6101</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Paine</t>
+          <t>Rancagua</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -5919,7 +5919,7 @@
         </is>
       </c>
       <c r="I121">
-        <v>51.56433</v>
+        <v>51.83538</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -5941,12 +5941,12 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>5603</t>
+          <t>5103</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>Concón</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -5965,7 +5965,7 @@
         </is>
       </c>
       <c r="I122">
-        <v>51.36162</v>
+        <v>51.731</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
@@ -5978,21 +5978,21 @@
         <v>2021</v>
       </c>
       <c r="B123">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>5605</t>
+          <t>13117</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>El Tabo</t>
+          <t>Lo Prado</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -6011,7 +6011,7 @@
         </is>
       </c>
       <c r="I123">
-        <v>51.30941</v>
+        <v>51.72179</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -6024,21 +6024,21 @@
         <v>2021</v>
       </c>
       <c r="B124">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>13104</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Conchalí</t>
+          <t>Quilpué</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -6057,7 +6057,7 @@
         </is>
       </c>
       <c r="I124">
-        <v>50.90141</v>
+        <v>51.60676</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>13504</t>
+          <t>13404</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>María Pinto</t>
+          <t>Paine</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -6103,7 +6103,7 @@
         </is>
       </c>
       <c r="I125">
-        <v>50.57361</v>
+        <v>51.56433</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -6116,21 +6116,21 @@
         <v>2021</v>
       </c>
       <c r="B126">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>6107</t>
+          <t>5603</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Las Cabras</t>
+          <t>Cartagena</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -6149,7 +6149,7 @@
         </is>
       </c>
       <c r="I126">
-        <v>50.06054</v>
+        <v>51.36162</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
@@ -6162,21 +6162,21 @@
         <v>2021</v>
       </c>
       <c r="B127">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>13110</t>
+          <t>5605</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>La Florida</t>
+          <t>El Tabo</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -6195,7 +6195,7 @@
         </is>
       </c>
       <c r="I127">
-        <v>49.87366</v>
+        <v>51.30941</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -6217,12 +6217,12 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>13604</t>
+          <t>13104</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Padre Hurtado</t>
+          <t>Conchalí</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -6241,7 +6241,7 @@
         </is>
       </c>
       <c r="I128">
-        <v>49.78731</v>
+        <v>50.90141</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
@@ -6254,21 +6254,21 @@
         <v>2021</v>
       </c>
       <c r="B129">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>6205</t>
+          <t>13504</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Navidad</t>
+          <t>María Pinto</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -6287,7 +6287,7 @@
         </is>
       </c>
       <c r="I129">
-        <v>49.2891</v>
+        <v>50.57361</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -6300,21 +6300,21 @@
         <v>2021</v>
       </c>
       <c r="B130">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>5101</t>
+          <t>6107</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Las Cabras</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="I130">
-        <v>49.07094</v>
+        <v>50.06054</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
@@ -6355,12 +6355,12 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>13501</t>
+          <t>13110</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Melipilla</t>
+          <t>La Florida</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -6379,7 +6379,7 @@
         </is>
       </c>
       <c r="I131">
-        <v>48.77251</v>
+        <v>49.87366</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
@@ -6401,12 +6401,12 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>13127</t>
+          <t>13604</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Padre Hurtado</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="I132">
-        <v>48.71748</v>
+        <v>49.78731</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
@@ -6447,12 +6447,12 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>6309</t>
+          <t>6205</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Pumanque</t>
+          <t>Navidad</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -6471,7 +6471,7 @@
         </is>
       </c>
       <c r="I133">
-        <v>48.57143</v>
+        <v>49.2891</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -6484,21 +6484,21 @@
         <v>2021</v>
       </c>
       <c r="B134">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>13109</t>
+          <t>5101</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>La Cisterna</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -6517,7 +6517,7 @@
         </is>
       </c>
       <c r="I134">
-        <v>48.03043</v>
+        <v>49.07094</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
@@ -6530,21 +6530,21 @@
         <v>2021</v>
       </c>
       <c r="B135">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>13501</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>El Quisco</t>
+          <t>Melipilla</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -6563,7 +6563,7 @@
         </is>
       </c>
       <c r="I135">
-        <v>47.78369</v>
+        <v>48.77251</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
@@ -6576,21 +6576,21 @@
         <v>2021</v>
       </c>
       <c r="B136">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>5109</t>
+          <t>13127</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Viña del Mar</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -6609,7 +6609,7 @@
         </is>
       </c>
       <c r="I136">
-        <v>47.62124</v>
+        <v>48.71748</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
@@ -6622,21 +6622,21 @@
         <v>2021</v>
       </c>
       <c r="B137">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>13402</t>
+          <t>6309</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Buin</t>
+          <t>Pumanque</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="I137">
-        <v>47.5773</v>
+        <v>48.57143</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
@@ -6668,21 +6668,21 @@
         <v>2021</v>
       </c>
       <c r="B138">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>6206</t>
+          <t>13109</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Paredones</t>
+          <t>La Cisterna</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="I138">
-        <v>47.36842</v>
+        <v>48.03043</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
@@ -6714,21 +6714,21 @@
         <v>2021</v>
       </c>
       <c r="B139">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>6201</t>
+          <t>5604</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Pichilemu</t>
+          <t>El Quisco</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -6747,7 +6747,7 @@
         </is>
       </c>
       <c r="I139">
-        <v>46.78572</v>
+        <v>47.78369</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
@@ -6760,21 +6760,21 @@
         <v>2021</v>
       </c>
       <c r="B140">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>13502</t>
+          <t>5109</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Alhué</t>
+          <t>Viña del Mar</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -6793,7 +6793,7 @@
         </is>
       </c>
       <c r="I140">
-        <v>45.86207</v>
+        <v>47.62124</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
@@ -6815,12 +6815,12 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>13126</t>
+          <t>13402</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Quinta Normal</t>
+          <t>Buin</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -6839,7 +6839,7 @@
         </is>
       </c>
       <c r="I141">
-        <v>45.43195</v>
+        <v>47.5773</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
@@ -6852,21 +6852,21 @@
         <v>2021</v>
       </c>
       <c r="B142">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>5602</t>
+          <t>6206</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Algarrobo</t>
+          <t>Paredones</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="I142">
-        <v>43.56435</v>
+        <v>47.36842</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
@@ -6898,21 +6898,21 @@
         <v>2021</v>
       </c>
       <c r="B143">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>13106</t>
+          <t>6201</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Estación Central</t>
+          <t>Pichilemu</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -6931,7 +6931,7 @@
         </is>
       </c>
       <c r="I143">
-        <v>42.5159</v>
+        <v>46.78572</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
@@ -6953,12 +6953,12 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>13130</t>
+          <t>13502</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Alhué</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="I144">
-        <v>41.39198</v>
+        <v>45.86207</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
@@ -6999,12 +6999,12 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>13108</t>
+          <t>13126</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Independencia</t>
+          <t>Quinta Normal</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -7023,7 +7023,7 @@
         </is>
       </c>
       <c r="I145">
-        <v>38.41003</v>
+        <v>45.43195</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
@@ -7036,21 +7036,21 @@
         <v>2021</v>
       </c>
       <c r="B146">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>13101</t>
+          <t>5602</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Algarrobo</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -7069,7 +7069,7 @@
         </is>
       </c>
       <c r="I146">
-        <v>38.28574</v>
+        <v>43.56435</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
@@ -7082,31 +7082,31 @@
         <v>2021</v>
       </c>
       <c r="B147">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>15201</t>
+          <t>13106</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Putre</t>
+          <t>Estación Central</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>norte</t>
+          <t>centro</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Macrozona Norte</t>
+          <t>Macrozona Centro</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -7115,7 +7115,7 @@
         </is>
       </c>
       <c r="I147">
-        <v>76.34408999999999</v>
+        <v>42.5159</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
@@ -7128,31 +7128,31 @@
         <v>2021</v>
       </c>
       <c r="B148">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>13130</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Freirina</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>norte</t>
+          <t>centro</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Macrozona Norte</t>
+          <t>Macrozona Centro</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="I148">
-        <v>68.55983999999999</v>
+        <v>41.39198</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
@@ -7174,31 +7174,31 @@
         <v>2021</v>
       </c>
       <c r="B149">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>13108</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Pica</t>
+          <t>Independencia</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>norte</t>
+          <t>centro</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Macrozona Norte</t>
+          <t>Macrozona Centro</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="I149">
-        <v>68.24034</v>
+        <v>38.41003</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
@@ -7220,31 +7220,31 @@
         <v>2021</v>
       </c>
       <c r="B150">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>13101</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Caldera</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>norte</t>
+          <t>centro</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Macrozona Norte</t>
+          <t>Macrozona Centro</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -7253,7 +7253,7 @@
         </is>
       </c>
       <c r="I150">
-        <v>66.9903</v>
+        <v>38.28574</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
@@ -7266,21 +7266,21 @@
         <v>2021</v>
       </c>
       <c r="B151">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>3304</t>
+          <t>15201</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Huasco</t>
+          <t>Putre</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="I151">
-        <v>66.62251999999999</v>
+        <v>76.34408999999999</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
@@ -7312,21 +7312,21 @@
         <v>2021</v>
       </c>
       <c r="B152">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>4305</t>
+          <t>3303</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Río Hurtado</t>
+          <t>Freirina</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -7345,7 +7345,7 @@
         </is>
       </c>
       <c r="I152">
-        <v>65.10417</v>
+        <v>68.55983999999999</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
@@ -7358,21 +7358,21 @@
         <v>2021</v>
       </c>
       <c r="B153">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>1405</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Chañaral</t>
+          <t>Pica</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -7391,7 +7391,7 @@
         </is>
       </c>
       <c r="I153">
-        <v>64.99477</v>
+        <v>68.24034</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
@@ -7404,21 +7404,21 @@
         <v>2021</v>
       </c>
       <c r="B154">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>4201</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Illapel</t>
+          <t>Caldera</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -7437,7 +7437,7 @@
         </is>
       </c>
       <c r="I154">
-        <v>63.35497</v>
+        <v>66.9903</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
@@ -7450,21 +7450,21 @@
         <v>2021</v>
       </c>
       <c r="B155">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>4103</t>
+          <t>3304</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Andacollo</t>
+          <t>Huasco</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -7483,7 +7483,7 @@
         </is>
       </c>
       <c r="I155">
-        <v>63.20755</v>
+        <v>66.62251999999999</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
@@ -7496,21 +7496,21 @@
         <v>2021</v>
       </c>
       <c r="B156">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>3301</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Vallenar</t>
+          <t>Río Hurtado</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -7529,7 +7529,7 @@
         </is>
       </c>
       <c r="I156">
-        <v>62.50354</v>
+        <v>65.10417</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
@@ -7542,21 +7542,21 @@
         <v>2021</v>
       </c>
       <c r="B157">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>4106</t>
+          <t>3201</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Vicuña</t>
+          <t>Chañaral</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -7575,7 +7575,7 @@
         </is>
       </c>
       <c r="I157">
-        <v>61.61369</v>
+        <v>64.99477</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
@@ -7597,12 +7597,12 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>4204</t>
+          <t>4201</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Salamanca</t>
+          <t>Illapel</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -7621,7 +7621,7 @@
         </is>
       </c>
       <c r="I158">
-        <v>61.42012</v>
+        <v>63.35497</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
@@ -7634,21 +7634,21 @@
         <v>2021</v>
       </c>
       <c r="B159">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2203</t>
+          <t>4103</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>San Pedro de Atacama</t>
+          <t>Andacollo</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -7667,7 +7667,7 @@
         </is>
       </c>
       <c r="I159">
-        <v>61.01469</v>
+        <v>63.20755</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
@@ -7680,21 +7680,21 @@
         <v>2021</v>
       </c>
       <c r="B160">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>15101</t>
+          <t>3301</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Arica</t>
+          <t>Vallenar</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -7713,7 +7713,7 @@
         </is>
       </c>
       <c r="I160">
-        <v>60.73632</v>
+        <v>62.50354</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
@@ -7735,12 +7735,12 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>4203</t>
+          <t>4106</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Los Vilos</t>
+          <t>Vicuña</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -7759,7 +7759,7 @@
         </is>
       </c>
       <c r="I161">
-        <v>58.86982</v>
+        <v>61.61369</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
@@ -7772,21 +7772,21 @@
         <v>2021</v>
       </c>
       <c r="B162">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>15202</t>
+          <t>4204</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>General Lagos</t>
+          <t>Salamanca</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -7805,7 +7805,7 @@
         </is>
       </c>
       <c r="I162">
-        <v>58.53658</v>
+        <v>61.42012</v>
       </c>
       <c r="J162" t="inlineStr">
         <is>
@@ -7818,21 +7818,21 @@
         <v>2021</v>
       </c>
       <c r="B163">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>2203</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>San Pedro de Atacama</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -7851,7 +7851,7 @@
         </is>
       </c>
       <c r="I163">
-        <v>57.80199</v>
+        <v>61.01469</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
@@ -7864,21 +7864,21 @@
         <v>2021</v>
       </c>
       <c r="B164">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>4301</t>
+          <t>15101</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Ovalle</t>
+          <t>Arica</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -7897,7 +7897,7 @@
         </is>
       </c>
       <c r="I164">
-        <v>57.72222</v>
+        <v>60.73632</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
@@ -7919,12 +7919,12 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>4104</t>
+          <t>4203</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>La Higuera</t>
+          <t>Los Vilos</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -7943,7 +7943,7 @@
         </is>
       </c>
       <c r="I165">
-        <v>57.28477</v>
+        <v>58.86982</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
@@ -7956,21 +7956,21 @@
         <v>2021</v>
       </c>
       <c r="B166">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>15202</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Combarbalá</t>
+          <t>General Lagos</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -7989,7 +7989,7 @@
         </is>
       </c>
       <c r="I166">
-        <v>57.22892</v>
+        <v>58.53658</v>
       </c>
       <c r="J166" t="inlineStr">
         <is>
@@ -8002,21 +8002,21 @@
         <v>2021</v>
       </c>
       <c r="B167">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>3103</t>
+          <t>4102</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Tierra Amarilla</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -8035,7 +8035,7 @@
         </is>
       </c>
       <c r="I167">
-        <v>56.99589</v>
+        <v>57.80199</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
@@ -8057,12 +8057,12 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>4304</t>
+          <t>4301</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Punitaqui</t>
+          <t>Ovalle</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -8081,7 +8081,7 @@
         </is>
       </c>
       <c r="I168">
-        <v>56.52174</v>
+        <v>57.72222</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
@@ -8103,12 +8103,12 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>4101</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>La Higuera</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -8127,7 +8127,7 @@
         </is>
       </c>
       <c r="I169">
-        <v>56.38049</v>
+        <v>57.28477</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
@@ -8140,21 +8140,21 @@
         <v>2021</v>
       </c>
       <c r="B170">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2103</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Sierra Gorda</t>
+          <t>Combarbalá</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -8173,7 +8173,7 @@
         </is>
       </c>
       <c r="I170">
-        <v>55.31915</v>
+        <v>57.22892</v>
       </c>
       <c r="J170" t="inlineStr">
         <is>
@@ -8186,21 +8186,21 @@
         <v>2021</v>
       </c>
       <c r="B171">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>4202</t>
+          <t>3103</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Canela</t>
+          <t>Tierra Amarilla</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="I171">
-        <v>54.15778</v>
+        <v>56.99589</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
@@ -8232,21 +8232,21 @@
         <v>2021</v>
       </c>
       <c r="B172">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>3101</t>
+          <t>4304</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Punitaqui</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -8265,7 +8265,7 @@
         </is>
       </c>
       <c r="I172">
-        <v>53.45691</v>
+        <v>56.52174</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
@@ -8278,21 +8278,21 @@
         <v>2021</v>
       </c>
       <c r="B173">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Mejillones</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -8311,7 +8311,7 @@
         </is>
       </c>
       <c r="I173">
-        <v>52.62712</v>
+        <v>56.38049</v>
       </c>
       <c r="J173" t="inlineStr">
         <is>
@@ -8324,21 +8324,21 @@
         <v>2021</v>
       </c>
       <c r="B174">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>2103</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Huara</t>
+          <t>Sierra Gorda</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -8357,7 +8357,7 @@
         </is>
       </c>
       <c r="I174">
-        <v>51.3834</v>
+        <v>55.31915</v>
       </c>
       <c r="J174" t="inlineStr">
         <is>
@@ -8370,31 +8370,31 @@
         <v>2021</v>
       </c>
       <c r="B175">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>9208</t>
+          <t>4202</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Purén</t>
+          <t>Canela</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>sur</t>
+          <t>norte</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Macrozona Sur</t>
+          <t>Macrozona Norte</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -8403,7 +8403,7 @@
         </is>
       </c>
       <c r="I175">
-        <v>70.8642</v>
+        <v>54.15778</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
@@ -8416,31 +8416,31 @@
         <v>2021</v>
       </c>
       <c r="B176">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>8312</t>
+          <t>3101</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Tucapel</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>sur</t>
+          <t>norte</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Macrozona Sur</t>
+          <t>Macrozona Norte</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -8449,7 +8449,7 @@
         </is>
       </c>
       <c r="I176">
-        <v>70.73761</v>
+        <v>53.45691</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
@@ -8462,31 +8462,31 @@
         <v>2021</v>
       </c>
       <c r="B177">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>9107</t>
+          <t>2102</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Gorbea</t>
+          <t>Mejillones</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>sur</t>
+          <t>norte</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Macrozona Sur</t>
+          <t>Macrozona Norte</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -8495,7 +8495,7 @@
         </is>
       </c>
       <c r="I177">
-        <v>70.24222</v>
+        <v>52.62712</v>
       </c>
       <c r="J177" t="inlineStr">
         <is>
@@ -8508,31 +8508,31 @@
         <v>2021</v>
       </c>
       <c r="B178">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>8202</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Arauco</t>
+          <t>Huara</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>sur</t>
+          <t>norte</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Macrozona Sur</t>
+          <t>Macrozona Norte</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="I178">
-        <v>68.49764999999999</v>
+        <v>51.3834</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
@@ -8563,12 +8563,12 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>9203</t>
+          <t>9208</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Curacautín</t>
+          <t>Purén</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -8587,7 +8587,7 @@
         </is>
       </c>
       <c r="I179">
-        <v>68.42104999999999</v>
+        <v>70.8642</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
@@ -8600,21 +8600,21 @@
         <v>2021</v>
       </c>
       <c r="B180">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>9201</t>
+          <t>8312</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Angol</t>
+          <t>Tucapel</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -8633,7 +8633,7 @@
         </is>
       </c>
       <c r="I180">
-        <v>67.86866000000001</v>
+        <v>70.73761</v>
       </c>
       <c r="J180" t="inlineStr">
         <is>
@@ -8655,12 +8655,12 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>9206</t>
+          <t>9107</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Los Sauces</t>
+          <t>Gorbea</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -8679,7 +8679,7 @@
         </is>
       </c>
       <c r="I181">
-        <v>67.48878999999999</v>
+        <v>70.24222</v>
       </c>
       <c r="J181" t="inlineStr">
         <is>
@@ -8692,21 +8692,21 @@
         <v>2021</v>
       </c>
       <c r="B182">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>10204</t>
+          <t>8202</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Curaco de Vélez</t>
+          <t>Arauco</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -8725,7 +8725,7 @@
         </is>
       </c>
       <c r="I182">
-        <v>67.37967999999999</v>
+        <v>68.49764999999999</v>
       </c>
       <c r="J182" t="inlineStr">
         <is>
@@ -8738,21 +8738,21 @@
         <v>2021</v>
       </c>
       <c r="B183">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>14107</t>
+          <t>9203</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Paillaco</t>
+          <t>Curacautín</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -8771,7 +8771,7 @@
         </is>
       </c>
       <c r="I183">
-        <v>67.04271</v>
+        <v>68.42104999999999</v>
       </c>
       <c r="J183" t="inlineStr">
         <is>
@@ -8784,21 +8784,21 @@
         <v>2021</v>
       </c>
       <c r="B184">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>9201</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Los Álamos</t>
+          <t>Angol</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -8817,7 +8817,7 @@
         </is>
       </c>
       <c r="I184">
-        <v>66.87457000000001</v>
+        <v>67.86866000000001</v>
       </c>
       <c r="J184" t="inlineStr">
         <is>
@@ -8830,21 +8830,21 @@
         <v>2021</v>
       </c>
       <c r="B185">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>14103</t>
+          <t>9206</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Lanco</t>
+          <t>Los Sauces</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="I185">
-        <v>66.72862000000001</v>
+        <v>67.48878999999999</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
@@ -8876,21 +8876,21 @@
         <v>2021</v>
       </c>
       <c r="B186">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>14201</t>
+          <t>10204</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>La Unión</t>
+          <t>Curaco de Vélez</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -8909,7 +8909,7 @@
         </is>
       </c>
       <c r="I186">
-        <v>66.15812</v>
+        <v>67.37967999999999</v>
       </c>
       <c r="J186" t="inlineStr">
         <is>
@@ -8922,21 +8922,21 @@
         <v>2021</v>
       </c>
       <c r="B187">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>10303</t>
+          <t>14107</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Purranque</t>
+          <t>Paillaco</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -8955,7 +8955,7 @@
         </is>
       </c>
       <c r="I187">
-        <v>66.13475</v>
+        <v>67.04271</v>
       </c>
       <c r="J187" t="inlineStr">
         <is>
@@ -8968,21 +8968,21 @@
         <v>2021</v>
       </c>
       <c r="B188">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>9210</t>
+          <t>8206</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Traiguén</t>
+          <t>Los Álamos</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -9001,7 +9001,7 @@
         </is>
       </c>
       <c r="I188">
-        <v>65.72353</v>
+        <v>66.87457000000001</v>
       </c>
       <c r="J188" t="inlineStr">
         <is>
@@ -9023,12 +9023,12 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>14105</t>
+          <t>14103</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Máfil</t>
+          <t>Lanco</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -9047,7 +9047,7 @@
         </is>
       </c>
       <c r="I189">
-        <v>65.64706</v>
+        <v>66.72862000000001</v>
       </c>
       <c r="J189" t="inlineStr">
         <is>
@@ -9069,12 +9069,12 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>14106</t>
+          <t>14201</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Mariquina</t>
+          <t>La Unión</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -9093,7 +9093,7 @@
         </is>
       </c>
       <c r="I190">
-        <v>65.61472999999999</v>
+        <v>66.15812</v>
       </c>
       <c r="J190" t="inlineStr">
         <is>
@@ -9106,21 +9106,21 @@
         <v>2021</v>
       </c>
       <c r="B191">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>9118</t>
+          <t>10303</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Toltén</t>
+          <t>Purranque</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -9139,7 +9139,7 @@
         </is>
       </c>
       <c r="I191">
-        <v>65.55944</v>
+        <v>66.13475</v>
       </c>
       <c r="J191" t="inlineStr">
         <is>
@@ -9152,21 +9152,21 @@
         <v>2021</v>
       </c>
       <c r="B192">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>10202</t>
+          <t>9210</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Ancud</t>
+          <t>Traiguén</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="I192">
-        <v>65.46948999999999</v>
+        <v>65.72353</v>
       </c>
       <c r="J192" t="inlineStr">
         <is>
@@ -9198,21 +9198,21 @@
         <v>2021</v>
       </c>
       <c r="B193">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>14105</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Perquenco</t>
+          <t>Máfil</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="I193">
-        <v>64.71861</v>
+        <v>65.64706</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
@@ -9244,21 +9244,21 @@
         <v>2021</v>
       </c>
       <c r="B194">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>9114</t>
+          <t>14106</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Pitrufquén</t>
+          <t>Mariquina</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -9277,7 +9277,7 @@
         </is>
       </c>
       <c r="I194">
-        <v>64.60235</v>
+        <v>65.61472999999999</v>
       </c>
       <c r="J194" t="inlineStr">
         <is>
@@ -9299,12 +9299,12 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>9211</t>
+          <t>9118</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Toltén</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -9323,7 +9323,7 @@
         </is>
       </c>
       <c r="I195">
-        <v>64.5069</v>
+        <v>65.55944</v>
       </c>
       <c r="J195" t="inlineStr">
         <is>
@@ -9336,21 +9336,21 @@
         <v>2021</v>
       </c>
       <c r="B196">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>9109</t>
+          <t>10202</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Loncoche</t>
+          <t>Ancud</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -9369,7 +9369,7 @@
         </is>
       </c>
       <c r="I196">
-        <v>64.46339</v>
+        <v>65.46948999999999</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
@@ -9382,21 +9382,21 @@
         <v>2021</v>
       </c>
       <c r="B197">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Hualaihué</t>
+          <t>Perquenco</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -9415,7 +9415,7 @@
         </is>
       </c>
       <c r="I197">
-        <v>64.19753</v>
+        <v>64.71861</v>
       </c>
       <c r="J197" t="inlineStr">
         <is>
@@ -9428,21 +9428,21 @@
         <v>2021</v>
       </c>
       <c r="B198">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>10210</t>
+          <t>9114</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Quinchao</t>
+          <t>Pitrufquén</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -9461,7 +9461,7 @@
         </is>
       </c>
       <c r="I198">
-        <v>64.13043999999999</v>
+        <v>64.60235</v>
       </c>
       <c r="J198" t="inlineStr">
         <is>
@@ -9474,21 +9474,21 @@
         <v>2021</v>
       </c>
       <c r="B199">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>10404</t>
+          <t>9211</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Palena</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -9507,7 +9507,7 @@
         </is>
       </c>
       <c r="I199">
-        <v>64</v>
+        <v>64.5069</v>
       </c>
       <c r="J199" t="inlineStr">
         <is>
@@ -9529,12 +9529,12 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>9209</t>
+          <t>9109</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Renaico</t>
+          <t>Loncoche</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -9553,7 +9553,7 @@
         </is>
       </c>
       <c r="I200">
-        <v>63.87363</v>
+        <v>64.46339</v>
       </c>
       <c r="J200" t="inlineStr">
         <is>
@@ -9566,21 +9566,21 @@
         <v>2021</v>
       </c>
       <c r="B201">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>8311</t>
+          <t>10403</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Santa Bárbara</t>
+          <t>Hualaihué</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -9599,7 +9599,7 @@
         </is>
       </c>
       <c r="I201">
-        <v>63.77491</v>
+        <v>64.19753</v>
       </c>
       <c r="J201" t="inlineStr">
         <is>
@@ -9612,21 +9612,21 @@
         <v>2021</v>
       </c>
       <c r="B202">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>8307</t>
+          <t>10210</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Negrete</t>
+          <t>Quinchao</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -9645,7 +9645,7 @@
         </is>
       </c>
       <c r="I202">
-        <v>63.05638</v>
+        <v>64.13043999999999</v>
       </c>
       <c r="J202" t="inlineStr">
         <is>
@@ -9658,21 +9658,21 @@
         <v>2021</v>
       </c>
       <c r="B203">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>8109</t>
+          <t>10404</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Santa Juana</t>
+          <t>Palena</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -9691,7 +9691,7 @@
         </is>
       </c>
       <c r="I203">
-        <v>62.89593</v>
+        <v>64</v>
       </c>
       <c r="J203" t="inlineStr">
         <is>
@@ -9704,21 +9704,21 @@
         <v>2021</v>
       </c>
       <c r="B204">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>8304</t>
+          <t>9209</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Laja</t>
+          <t>Renaico</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -9737,7 +9737,7 @@
         </is>
       </c>
       <c r="I204">
-        <v>62.85511</v>
+        <v>63.87363</v>
       </c>
       <c r="J204" t="inlineStr">
         <is>
@@ -9759,12 +9759,12 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>8106</t>
+          <t>8311</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Lota</t>
+          <t>Santa Bárbara</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -9783,7 +9783,7 @@
         </is>
       </c>
       <c r="I205">
-        <v>62.84299</v>
+        <v>63.77491</v>
       </c>
       <c r="J205" t="inlineStr">
         <is>
@@ -9796,21 +9796,21 @@
         <v>2021</v>
       </c>
       <c r="B206">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>9102</t>
+          <t>8307</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Carahue</t>
+          <t>Negrete</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -9829,7 +9829,7 @@
         </is>
       </c>
       <c r="I206">
-        <v>62.83573</v>
+        <v>63.05638</v>
       </c>
       <c r="J206" t="inlineStr">
         <is>
@@ -9842,21 +9842,21 @@
         <v>2021</v>
       </c>
       <c r="B207">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>10106</t>
+          <t>8109</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Los Muermos</t>
+          <t>Santa Juana</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -9875,7 +9875,7 @@
         </is>
       </c>
       <c r="I207">
-        <v>62.80242</v>
+        <v>62.89593</v>
       </c>
       <c r="J207" t="inlineStr">
         <is>
@@ -9897,12 +9897,12 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>8310</t>
+          <t>8304</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>San Rosendo</t>
+          <t>Laja</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -9921,7 +9921,7 @@
         </is>
       </c>
       <c r="I208">
-        <v>62.7907</v>
+        <v>62.85511</v>
       </c>
       <c r="J208" t="inlineStr">
         <is>
@@ -9934,21 +9934,21 @@
         <v>2021</v>
       </c>
       <c r="B209">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>10206</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Puqueldón</t>
+          <t>Lota</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -9967,7 +9967,7 @@
         </is>
       </c>
       <c r="I209">
-        <v>62.70271</v>
+        <v>62.84299</v>
       </c>
       <c r="J209" t="inlineStr">
         <is>
@@ -9980,21 +9980,21 @@
         <v>2021</v>
       </c>
       <c r="B210">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>10104</t>
+          <t>9102</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Fresia</t>
+          <t>Carahue</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -10013,7 +10013,7 @@
         </is>
       </c>
       <c r="I210">
-        <v>62.68436</v>
+        <v>62.83573</v>
       </c>
       <c r="J210" t="inlineStr">
         <is>
@@ -10035,12 +10035,12 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>10106</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Osorno</t>
+          <t>Los Muermos</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -10059,7 +10059,7 @@
         </is>
       </c>
       <c r="I211">
-        <v>62.61465</v>
+        <v>62.80242</v>
       </c>
       <c r="J211" t="inlineStr">
         <is>
@@ -10072,21 +10072,21 @@
         <v>2021</v>
       </c>
       <c r="B212">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>14101</t>
+          <t>8310</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Valdivia</t>
+          <t>San Rosendo</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -10105,7 +10105,7 @@
         </is>
       </c>
       <c r="I212">
-        <v>62.35294</v>
+        <v>62.7907</v>
       </c>
       <c r="J212" t="inlineStr">
         <is>
@@ -10127,12 +10127,12 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>10108</t>
+          <t>10206</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Maullín</t>
+          <t>Puqueldón</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -10151,7 +10151,7 @@
         </is>
       </c>
       <c r="I213">
-        <v>62.34719</v>
+        <v>62.70271</v>
       </c>
       <c r="J213" t="inlineStr">
         <is>
@@ -10164,21 +10164,21 @@
         <v>2021</v>
       </c>
       <c r="B214">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>10104</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Fresia</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -10197,7 +10197,7 @@
         </is>
       </c>
       <c r="I214">
-        <v>62.22392</v>
+        <v>62.68436</v>
       </c>
       <c r="J214" t="inlineStr">
         <is>
@@ -10210,21 +10210,21 @@
         <v>2021</v>
       </c>
       <c r="B215">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>9103</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Cunco</t>
+          <t>Osorno</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -10243,7 +10243,7 @@
         </is>
       </c>
       <c r="I215">
-        <v>62.21498</v>
+        <v>62.61465</v>
       </c>
       <c r="J215" t="inlineStr">
         <is>
@@ -10256,21 +10256,21 @@
         <v>2021</v>
       </c>
       <c r="B216">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>9204</t>
+          <t>14101</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Ercilla</t>
+          <t>Valdivia</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -10289,7 +10289,7 @@
         </is>
       </c>
       <c r="I216">
-        <v>62.18612</v>
+        <v>62.35294</v>
       </c>
       <c r="J216" t="inlineStr">
         <is>
@@ -10302,21 +10302,21 @@
         <v>2021</v>
       </c>
       <c r="B217">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>8308</t>
+          <t>10108</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Quilaco</t>
+          <t>Maullín</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -10335,7 +10335,7 @@
         </is>
       </c>
       <c r="I217">
-        <v>61.94332</v>
+        <v>62.34719</v>
       </c>
       <c r="J217" t="inlineStr">
         <is>
@@ -10348,23 +10348,23 @@
         <v>2021</v>
       </c>
       <c r="B218">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
           <t>Los Lagos</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>10107</t>
-        </is>
-      </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>Llanquihue</t>
-        </is>
-      </c>
       <c r="F218" t="inlineStr">
         <is>
           <t>sur</t>
@@ -10381,7 +10381,7 @@
         </is>
       </c>
       <c r="I218">
-        <v>61.81641</v>
+        <v>62.22392</v>
       </c>
       <c r="J218" t="inlineStr">
         <is>
@@ -10394,21 +10394,21 @@
         <v>2021</v>
       </c>
       <c r="B219">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>8107</t>
+          <t>9103</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Penco</t>
+          <t>Cunco</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -10427,7 +10427,7 @@
         </is>
       </c>
       <c r="I219">
-        <v>61.77004</v>
+        <v>62.21498</v>
       </c>
       <c r="J219" t="inlineStr">
         <is>
@@ -10440,21 +10440,21 @@
         <v>2021</v>
       </c>
       <c r="B220">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>10307</t>
+          <t>9204</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>San Pablo</t>
+          <t>Ercilla</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -10473,7 +10473,7 @@
         </is>
       </c>
       <c r="I220">
-        <v>61.64383</v>
+        <v>62.18612</v>
       </c>
       <c r="J220" t="inlineStr">
         <is>
@@ -10486,21 +10486,21 @@
         <v>2021</v>
       </c>
       <c r="B221">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>10101</t>
+          <t>8308</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Quilaco</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -10519,7 +10519,7 @@
         </is>
       </c>
       <c r="I221">
-        <v>61.51032</v>
+        <v>61.94332</v>
       </c>
       <c r="J221" t="inlineStr">
         <is>
@@ -10532,21 +10532,21 @@
         <v>2021</v>
       </c>
       <c r="B222">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>9111</t>
+          <t>10107</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Nueva Imperial</t>
+          <t>Llanquihue</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -10565,7 +10565,7 @@
         </is>
       </c>
       <c r="I222">
-        <v>61.00196</v>
+        <v>61.81641</v>
       </c>
       <c r="J222" t="inlineStr">
         <is>
@@ -10587,12 +10587,12 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>8111</t>
+          <t>8107</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Tomé</t>
+          <t>Penco</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -10611,7 +10611,7 @@
         </is>
       </c>
       <c r="I223">
-        <v>60.93544</v>
+        <v>61.77004</v>
       </c>
       <c r="J223" t="inlineStr">
         <is>
@@ -10624,21 +10624,21 @@
         <v>2021</v>
       </c>
       <c r="B224">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>14102</t>
+          <t>10307</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Corral</t>
+          <t>San Pablo</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -10657,7 +10657,7 @@
         </is>
       </c>
       <c r="I224">
-        <v>60.8209</v>
+        <v>61.64383</v>
       </c>
       <c r="J224" t="inlineStr">
         <is>
@@ -10670,21 +10670,21 @@
         <v>2021</v>
       </c>
       <c r="B225">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>8105</t>
+          <t>10101</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Hualqui</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -10703,7 +10703,7 @@
         </is>
       </c>
       <c r="I225">
-        <v>60.64042</v>
+        <v>61.51032</v>
       </c>
       <c r="J225" t="inlineStr">
         <is>
@@ -10716,21 +10716,21 @@
         <v>2021</v>
       </c>
       <c r="B226">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>9111</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Coronel</t>
+          <t>Nueva Imperial</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -10749,7 +10749,7 @@
         </is>
       </c>
       <c r="I226">
-        <v>60.38961</v>
+        <v>61.00196</v>
       </c>
       <c r="J226" t="inlineStr">
         <is>
@@ -10762,21 +10762,21 @@
         <v>2021</v>
       </c>
       <c r="B227">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>9202</t>
+          <t>8111</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Collipulli</t>
+          <t>Tomé</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -10795,7 +10795,7 @@
         </is>
       </c>
       <c r="I227">
-        <v>60.28065</v>
+        <v>60.93544</v>
       </c>
       <c r="J227" t="inlineStr">
         <is>
@@ -10808,21 +10808,21 @@
         <v>2021</v>
       </c>
       <c r="B228">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>9119</t>
+          <t>14102</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Vilcún</t>
+          <t>Corral</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -10841,7 +10841,7 @@
         </is>
       </c>
       <c r="I228">
-        <v>60.24691</v>
+        <v>60.8209</v>
       </c>
       <c r="J228" t="inlineStr">
         <is>
@@ -10863,12 +10863,12 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>8306</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Nacimiento</t>
+          <t>Hualqui</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -10887,7 +10887,7 @@
         </is>
       </c>
       <c r="I229">
-        <v>59.65559</v>
+        <v>60.64042</v>
       </c>
       <c r="J229" t="inlineStr">
         <is>
@@ -10909,12 +10909,12 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Coronel</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -10933,7 +10933,7 @@
         </is>
       </c>
       <c r="I230">
-        <v>59.36</v>
+        <v>60.38961</v>
       </c>
       <c r="J230" t="inlineStr">
         <is>
@@ -10955,12 +10955,12 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>9108</t>
+          <t>9202</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Lautaro</t>
+          <t>Collipulli</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -10979,7 +10979,7 @@
         </is>
       </c>
       <c r="I231">
-        <v>59.34066</v>
+        <v>60.28065</v>
       </c>
       <c r="J231" t="inlineStr">
         <is>
@@ -10992,21 +10992,21 @@
         <v>2021</v>
       </c>
       <c r="B232">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>8309</t>
+          <t>9119</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Quilleco</t>
+          <t>Vilcún</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -11025,7 +11025,7 @@
         </is>
       </c>
       <c r="I232">
-        <v>59.15221</v>
+        <v>60.24691</v>
       </c>
       <c r="J232" t="inlineStr">
         <is>
@@ -11038,21 +11038,21 @@
         <v>2021</v>
       </c>
       <c r="B233">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>10304</t>
+          <t>8306</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Puyehue</t>
+          <t>Nacimiento</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -11071,7 +11071,7 @@
         </is>
       </c>
       <c r="I233">
-        <v>59.10653</v>
+        <v>59.65559</v>
       </c>
       <c r="J233" t="inlineStr">
         <is>
@@ -11084,21 +11084,21 @@
         <v>2021</v>
       </c>
       <c r="B234">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>9101</t>
+          <t>8104</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Temuco</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -11117,7 +11117,7 @@
         </is>
       </c>
       <c r="I234">
-        <v>59.05146</v>
+        <v>59.36</v>
       </c>
       <c r="J234" t="inlineStr">
         <is>
@@ -11130,21 +11130,21 @@
         <v>2021</v>
       </c>
       <c r="B235">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>10209</t>
+          <t>9108</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Quemchi</t>
+          <t>Lautaro</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -11163,7 +11163,7 @@
         </is>
       </c>
       <c r="I235">
-        <v>58.94207</v>
+        <v>59.34066</v>
       </c>
       <c r="J235" t="inlineStr">
         <is>
@@ -11176,21 +11176,21 @@
         <v>2021</v>
       </c>
       <c r="B236">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>9112</t>
+          <t>8309</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Padre Las Casas</t>
+          <t>Quilleco</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -11209,7 +11209,7 @@
         </is>
       </c>
       <c r="I236">
-        <v>58.82013</v>
+        <v>59.15221</v>
       </c>
       <c r="J236" t="inlineStr">
         <is>
@@ -11222,21 +11222,21 @@
         <v>2021</v>
       </c>
       <c r="B237">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>9110</t>
+          <t>10304</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Melipeuco</t>
+          <t>Puyehue</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -11255,7 +11255,7 @@
         </is>
       </c>
       <c r="I237">
-        <v>58.80952</v>
+        <v>59.10653</v>
       </c>
       <c r="J237" t="inlineStr">
         <is>
@@ -11268,21 +11268,21 @@
         <v>2021</v>
       </c>
       <c r="B238">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>10305</t>
+          <t>9101</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Río Negro</t>
+          <t>Temuco</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -11301,7 +11301,7 @@
         </is>
       </c>
       <c r="I238">
-        <v>58.69565</v>
+        <v>59.05146</v>
       </c>
       <c r="J238" t="inlineStr">
         <is>
@@ -11314,21 +11314,21 @@
         <v>2021</v>
       </c>
       <c r="B239">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>9104</t>
+          <t>10209</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Curarrehue</t>
+          <t>Quemchi</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -11347,7 +11347,7 @@
         </is>
       </c>
       <c r="I239">
-        <v>58.39161</v>
+        <v>58.94207</v>
       </c>
       <c r="J239" t="inlineStr">
         <is>
@@ -11360,21 +11360,21 @@
         <v>2021</v>
       </c>
       <c r="B240">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>8203</t>
+          <t>9112</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Cañete</t>
+          <t>Padre Las Casas</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -11393,7 +11393,7 @@
         </is>
       </c>
       <c r="I240">
-        <v>58.01724</v>
+        <v>58.82013</v>
       </c>
       <c r="J240" t="inlineStr">
         <is>
@@ -11406,21 +11406,21 @@
         <v>2021</v>
       </c>
       <c r="B241">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>8303</t>
+          <t>9110</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Cabrero</t>
+          <t>Melipeuco</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -11439,7 +11439,7 @@
         </is>
       </c>
       <c r="I241">
-        <v>57.47562</v>
+        <v>58.80952</v>
       </c>
       <c r="J241" t="inlineStr">
         <is>
@@ -11461,12 +11461,12 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>10205</t>
+          <t>10305</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Dalcahue</t>
+          <t>Río Negro</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -11485,7 +11485,7 @@
         </is>
       </c>
       <c r="I242">
-        <v>57.36961</v>
+        <v>58.69565</v>
       </c>
       <c r="J242" t="inlineStr">
         <is>
@@ -11498,21 +11498,21 @@
         <v>2021</v>
       </c>
       <c r="B243">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>10207</t>
+          <t>9104</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Queilén</t>
+          <t>Curarrehue</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -11531,7 +11531,7 @@
         </is>
       </c>
       <c r="I243">
-        <v>57.24138</v>
+        <v>58.39161</v>
       </c>
       <c r="J243" t="inlineStr">
         <is>
@@ -11544,21 +11544,21 @@
         <v>2021</v>
       </c>
       <c r="B244">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>10102</t>
+          <t>8203</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Calbuco</t>
+          <t>Cañete</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -11577,7 +11577,7 @@
         </is>
       </c>
       <c r="I244">
-        <v>57.109</v>
+        <v>58.01724</v>
       </c>
       <c r="J244" t="inlineStr">
         <is>
@@ -11590,21 +11590,21 @@
         <v>2021</v>
       </c>
       <c r="B245">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>9105</t>
+          <t>8303</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Freire</t>
+          <t>Cabrero</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -11623,7 +11623,7 @@
         </is>
       </c>
       <c r="I245">
-        <v>56.68563</v>
+        <v>57.47562</v>
       </c>
       <c r="J245" t="inlineStr">
         <is>
@@ -11636,21 +11636,21 @@
         <v>2021</v>
       </c>
       <c r="B246">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>8103</t>
+          <t>10205</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Chiguayante</t>
+          <t>Dalcahue</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -11669,7 +11669,7 @@
         </is>
       </c>
       <c r="I246">
-        <v>56.62701</v>
+        <v>57.36961</v>
       </c>
       <c r="J246" t="inlineStr">
         <is>
@@ -11691,12 +11691,12 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>10203</t>
+          <t>10207</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Chonchi</t>
+          <t>Queilén</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -11715,7 +11715,7 @@
         </is>
       </c>
       <c r="I247">
-        <v>56.53631</v>
+        <v>57.24138</v>
       </c>
       <c r="J247" t="inlineStr">
         <is>
@@ -11728,21 +11728,21 @@
         <v>2021</v>
       </c>
       <c r="B248">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>9117</t>
+          <t>10102</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Teodoro Schmidt</t>
+          <t>Calbuco</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -11761,7 +11761,7 @@
         </is>
       </c>
       <c r="I248">
-        <v>56.4868</v>
+        <v>57.109</v>
       </c>
       <c r="J248" t="inlineStr">
         <is>
@@ -11774,21 +11774,21 @@
         <v>2021</v>
       </c>
       <c r="B249">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>8108</t>
+          <t>9105</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>San Pedro de la Paz</t>
+          <t>Freire</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -11807,7 +11807,7 @@
         </is>
       </c>
       <c r="I249">
-        <v>56.12526</v>
+        <v>56.68563</v>
       </c>
       <c r="J249" t="inlineStr">
         <is>
@@ -11820,21 +11820,21 @@
         <v>2021</v>
       </c>
       <c r="B250">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>9205</t>
+          <t>8103</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Lonquimay</t>
+          <t>Chiguayante</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -11853,7 +11853,7 @@
         </is>
       </c>
       <c r="I250">
-        <v>56.03985</v>
+        <v>56.62701</v>
       </c>
       <c r="J250" t="inlineStr">
         <is>
@@ -11866,21 +11866,21 @@
         <v>2021</v>
       </c>
       <c r="B251">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>10203</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Villarrica</t>
+          <t>Chonchi</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -11899,7 +11899,7 @@
         </is>
       </c>
       <c r="I251">
-        <v>56.01783</v>
+        <v>56.53631</v>
       </c>
       <c r="J251" t="inlineStr">
         <is>
@@ -11912,21 +11912,21 @@
         <v>2021</v>
       </c>
       <c r="B252">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>8204</t>
+          <t>9117</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Contulmo</t>
+          <t>Teodoro Schmidt</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -11945,7 +11945,7 @@
         </is>
       </c>
       <c r="I252">
-        <v>55.8642</v>
+        <v>56.4868</v>
       </c>
       <c r="J252" t="inlineStr">
         <is>
@@ -11958,21 +11958,21 @@
         <v>2021</v>
       </c>
       <c r="B253">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>14203</t>
+          <t>8108</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Lago Ranco</t>
+          <t>San Pedro de la Paz</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -11991,7 +11991,7 @@
         </is>
       </c>
       <c r="I253">
-        <v>55.53957</v>
+        <v>56.12526</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -12004,21 +12004,21 @@
         <v>2021</v>
       </c>
       <c r="B254">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>10201</t>
+          <t>9205</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Castro</t>
+          <t>Lonquimay</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="I254">
-        <v>55.22594</v>
+        <v>56.03985</v>
       </c>
       <c r="J254" t="inlineStr">
         <is>
@@ -12050,21 +12050,21 @@
         <v>2021</v>
       </c>
       <c r="B255">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>10109</t>
+          <t>9120</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Puerto Varas</t>
+          <t>Villarrica</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -12083,7 +12083,7 @@
         </is>
       </c>
       <c r="I255">
-        <v>55.21777</v>
+        <v>56.01783</v>
       </c>
       <c r="J255" t="inlineStr">
         <is>
@@ -12105,12 +12105,12 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>8204</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Talcahuano</t>
+          <t>Contulmo</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -12129,7 +12129,7 @@
         </is>
       </c>
       <c r="I256">
-        <v>55.19197</v>
+        <v>55.8642</v>
       </c>
       <c r="J256" t="inlineStr">
         <is>
@@ -12142,21 +12142,21 @@
         <v>2021</v>
       </c>
       <c r="B257">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>8301</t>
+          <t>14203</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Los Ángeles</t>
+          <t>Lago Ranco</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -12175,7 +12175,7 @@
         </is>
       </c>
       <c r="I257">
-        <v>55.13966</v>
+        <v>55.53957</v>
       </c>
       <c r="J257" t="inlineStr">
         <is>
@@ -12188,21 +12188,21 @@
         <v>2021</v>
       </c>
       <c r="B258">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>9106</t>
+          <t>10201</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Galvarino</t>
+          <t>Castro</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -12221,7 +12221,7 @@
         </is>
       </c>
       <c r="I258">
-        <v>55.03106</v>
+        <v>55.22594</v>
       </c>
       <c r="J258" t="inlineStr">
         <is>
@@ -12234,21 +12234,21 @@
         <v>2021</v>
       </c>
       <c r="B259">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>14108</t>
+          <t>10109</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Panguipulli</t>
+          <t>Puerto Varas</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -12267,7 +12267,7 @@
         </is>
       </c>
       <c r="I259">
-        <v>54.95194</v>
+        <v>55.21777</v>
       </c>
       <c r="J259" t="inlineStr">
         <is>
@@ -12280,21 +12280,21 @@
         <v>2021</v>
       </c>
       <c r="B260">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>9121</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Cholchol</t>
+          <t>Talcahuano</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -12313,7 +12313,7 @@
         </is>
       </c>
       <c r="I260">
-        <v>54.73301</v>
+        <v>55.19197</v>
       </c>
       <c r="J260" t="inlineStr">
         <is>
@@ -12326,21 +12326,21 @@
         <v>2021</v>
       </c>
       <c r="B261">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>14202</t>
+          <t>8301</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Futrono</t>
+          <t>Los Ángeles</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -12359,7 +12359,7 @@
         </is>
       </c>
       <c r="I261">
-        <v>54.64015</v>
+        <v>55.13966</v>
       </c>
       <c r="J261" t="inlineStr">
         <is>
@@ -12372,21 +12372,21 @@
         <v>2021</v>
       </c>
       <c r="B262">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>8207</t>
+          <t>9106</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Tirúa</t>
+          <t>Galvarino</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -12405,7 +12405,7 @@
         </is>
       </c>
       <c r="I262">
-        <v>54.52055</v>
+        <v>55.03106</v>
       </c>
       <c r="J262" t="inlineStr">
         <is>
@@ -12418,21 +12418,21 @@
         <v>2021</v>
       </c>
       <c r="B263">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>10105</t>
+          <t>14108</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Frutillar</t>
+          <t>Panguipulli</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -12451,7 +12451,7 @@
         </is>
       </c>
       <c r="I263">
-        <v>54.46355</v>
+        <v>54.95194</v>
       </c>
       <c r="J263" t="inlineStr">
         <is>
@@ -12464,21 +12464,21 @@
         <v>2021</v>
       </c>
       <c r="B264">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>9121</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Cholchol</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -12497,7 +12497,7 @@
         </is>
       </c>
       <c r="I264">
-        <v>53.83811</v>
+        <v>54.73301</v>
       </c>
       <c r="J264" t="inlineStr">
         <is>
@@ -12510,21 +12510,21 @@
         <v>2021</v>
       </c>
       <c r="B265">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>10402</t>
+          <t>14202</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Futaleufú</t>
+          <t>Futrono</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -12543,7 +12543,7 @@
         </is>
       </c>
       <c r="I265">
-        <v>53.0303</v>
+        <v>54.64015</v>
       </c>
       <c r="J265" t="inlineStr">
         <is>
@@ -12565,12 +12565,12 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>8313</t>
+          <t>8207</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Yumbel</t>
+          <t>Tirúa</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -12589,7 +12589,7 @@
         </is>
       </c>
       <c r="I266">
-        <v>52.65781</v>
+        <v>54.52055</v>
       </c>
       <c r="J266" t="inlineStr">
         <is>
@@ -12602,21 +12602,21 @@
         <v>2021</v>
       </c>
       <c r="B267">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>9115</t>
+          <t>10105</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Pucón</t>
+          <t>Frutillar</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -12635,7 +12635,7 @@
         </is>
       </c>
       <c r="I267">
-        <v>52.14074</v>
+        <v>54.46355</v>
       </c>
       <c r="J267" t="inlineStr">
         <is>
@@ -12648,21 +12648,21 @@
         <v>2021</v>
       </c>
       <c r="B268">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>10302</t>
+          <t>8101</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Puerto Octay</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -12681,7 +12681,7 @@
         </is>
       </c>
       <c r="I268">
-        <v>51.28205</v>
+        <v>53.83811</v>
       </c>
       <c r="J268" t="inlineStr">
         <is>
@@ -12694,21 +12694,21 @@
         <v>2021</v>
       </c>
       <c r="B269">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>9116</t>
+          <t>10402</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Futaleufú</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -12727,7 +12727,7 @@
         </is>
       </c>
       <c r="I269">
-        <v>51.12782</v>
+        <v>53.0303</v>
       </c>
       <c r="J269" t="inlineStr">
         <is>
@@ -12740,21 +12740,21 @@
         <v>2021</v>
       </c>
       <c r="B270">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>10208</t>
+          <t>8313</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Quellón</t>
+          <t>Yumbel</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -12773,7 +12773,7 @@
         </is>
       </c>
       <c r="I270">
-        <v>50.37898</v>
+        <v>52.65781</v>
       </c>
       <c r="J270" t="inlineStr">
         <is>
@@ -12786,21 +12786,21 @@
         <v>2021</v>
       </c>
       <c r="B271">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>10103</t>
+          <t>9115</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Cochamó</t>
+          <t>Pucón</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -12819,7 +12819,7 @@
         </is>
       </c>
       <c r="I271">
-        <v>50.22625</v>
+        <v>52.14074</v>
       </c>
       <c r="J271" t="inlineStr">
         <is>
@@ -12841,12 +12841,12 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>10306</t>
+          <t>10302</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>San Juan de la Costa</t>
+          <t>Puerto Octay</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -12865,7 +12865,7 @@
         </is>
       </c>
       <c r="I272">
-        <v>48.0663</v>
+        <v>51.28205</v>
       </c>
       <c r="J272" t="inlineStr">
         <is>
@@ -12878,21 +12878,21 @@
         <v>2021</v>
       </c>
       <c r="B273">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>8302</t>
+          <t>9116</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Antuco</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -12911,7 +12911,7 @@
         </is>
       </c>
       <c r="I273">
-        <v>48.0315</v>
+        <v>51.12782</v>
       </c>
       <c r="J273" t="inlineStr">
         <is>
@@ -12933,33 +12933,217 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
+          <t>10208</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Quellón</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>sur</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Macrozona Sur</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>E_PRENETA_a</t>
+        </is>
+      </c>
+      <c r="I274">
+        <v>50.37898</v>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>Tasa neta preescolar</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275">
+        <v>2021</v>
+      </c>
+      <c r="B275">
+        <v>10</v>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>10103</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Cochamó</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>sur</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>Macrozona Sur</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>E_PRENETA_a</t>
+        </is>
+      </c>
+      <c r="I275">
+        <v>50.22625</v>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>Tasa neta preescolar</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276">
+        <v>2021</v>
+      </c>
+      <c r="B276">
+        <v>10</v>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>10306</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>San Juan de la Costa</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>sur</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Macrozona Sur</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>E_PRENETA_a</t>
+        </is>
+      </c>
+      <c r="I276">
+        <v>48.0663</v>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>Tasa neta preescolar</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277">
+        <v>2021</v>
+      </c>
+      <c r="B277">
+        <v>8</v>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>8302</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Antuco</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>sur</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Macrozona Sur</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>E_PRENETA_a</t>
+        </is>
+      </c>
+      <c r="I277">
+        <v>48.0315</v>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>Tasa neta preescolar</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278">
+        <v>2021</v>
+      </c>
+      <c r="B278">
+        <v>10</v>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
           <t>10401</t>
         </is>
       </c>
-      <c r="E274" t="inlineStr">
+      <c r="E278" t="inlineStr">
         <is>
           <t>Chaitén</t>
         </is>
       </c>
-      <c r="F274" t="inlineStr">
+      <c r="F278" t="inlineStr">
         <is>
           <t>sur</t>
         </is>
       </c>
-      <c r="G274" t="inlineStr">
+      <c r="G278" t="inlineStr">
         <is>
           <t>Macrozona Sur</t>
         </is>
       </c>
-      <c r="H274" t="inlineStr">
-        <is>
-          <t>E_PRENETA_a</t>
-        </is>
-      </c>
-      <c r="I274">
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>E_PRENETA_a</t>
+        </is>
+      </c>
+      <c r="I278">
         <v>46.55172</v>
       </c>
-      <c r="J274" t="inlineStr">
+      <c r="J278" t="inlineStr">
         <is>
           <t>Tasa neta preescolar</t>
         </is>

--- a/output/graficos_nacionales/plot_nacional_e_preneta_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_preneta_a_2021.xlsx
@@ -416,7 +416,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -462,7 +462,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -508,7 +508,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -8650,7 +8650,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -8696,7 +8696,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -8742,7 +8742,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -8972,7 +8972,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -9248,7 +9248,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -9294,7 +9294,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -9432,7 +9432,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -9478,7 +9478,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -9708,7 +9708,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -9754,7 +9754,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -9846,7 +9846,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -9892,7 +9892,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -10076,7 +10076,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -10260,7 +10260,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -10352,7 +10352,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -10398,7 +10398,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -10490,7 +10490,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -10582,7 +10582,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -10812,7 +10812,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -12100,7 +12100,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -12330,7 +12330,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -12468,7 +12468,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -12652,7 +12652,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -12790,7 +12790,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -12882,7 +12882,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">

--- a/output/graficos_nacionales/plot_nacional_e_preneta_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_preneta_a_2021.xlsx
@@ -1789,7 +1789,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:47</t>
+    <t xml:space="preserve">2026-09-07 12:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_e_preneta_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_preneta_a_2021.xlsx
@@ -1789,7 +1789,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:52</t>
+    <t xml:space="preserve">2026-09-08 10:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
